--- a/curation_benchmark/results/supp_tables/supp_table_ROC_AUC.xlsx
+++ b/curation_benchmark/results/supp_tables/supp_table_ROC_AUC.xlsx
@@ -1,40 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ADRD (80%)" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="ASD (80%)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ASD_excl_ClinVar (80%)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="CHD (80%)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="CHD_excl_ClinVar (80%)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="DDD (80%)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="DDD_excl_ClinVar (80%)" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Cancer_MSK (80%)" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Cancer_TCGA (80%)" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Cancer_AlphaMissense (80%)" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="ClinVar_Balanced (80%)" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="ClinVar_Onestar+ (80%)" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="ClinVar_Twostar+ (80%)" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="ClinVar_Threestar+ (80%)" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="ADRD (90%)" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="ASD (90%)" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="ASD_excl_ClinVar (90%)" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="CHD (90%)" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="CHD_excl_ClinVar (90%)" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="DDD (90%)" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="DDD_excl_ClinVar (90%)" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Cancer_MSK (90%)" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Cancer_TCGA (90%)" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Cancer_AlphaMissense (90%)" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="ClinVar_Balanced (90%)" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="ClinVar_Onestar+ (90%)" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="ClinVar_Twostar+ (90%)" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="ClinVar_Threestar+ (90%)" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ADRD (80%)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ASD (80%)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ASD_excl_ClinVar (80%)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHD (80%)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHD_excl_ClinVar (80%)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DDD (80%)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DDD_excl_ClinVar (80%)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cancer_MSK (80%)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cancer_TCGA (80%)" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cancer_AlphaMissense (80%)" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ClinVar_Balanced (80%)" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ClinVar_Onestar+ (80%)" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ClinVar_Twostar+ (80%)" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ClinVar_Threestar+ (80%)" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ADRD (90%)" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ASD (90%)" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ASD_excl_ClinVar (90%)" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHD (90%)" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHD_excl_ClinVar (90%)" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DDD (90%)" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DDD_excl_ClinVar (90%)" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cancer_MSK (90%)" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cancer_TCGA (90%)" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cancer_AlphaMissense (90%)" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ClinVar_Balanced (90%)" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ClinVar_Onestar+ (90%)" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ClinVar_Twostar+ (90%)" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ClinVar_Threestar+ (90%)" sheetId="28" state="visible" r:id="rId28"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1864,7 +1864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2172,11 +2172,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>PROVEAN</t>
+          <t>Eigen-raw_coding</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.8972366340091866</v>
+        <v>0.8990248126026686</v>
       </c>
     </row>
     <row r="17">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Polyphen2_HVAR</t>
+          <t>PROVEAN</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.8952179141713039</v>
+        <v>0.8972366340091866</v>
       </c>
     </row>
     <row r="18">
@@ -2210,11 +2210,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ESM1b</t>
+          <t>Polyphen2_HVAR</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.8925839592547476</v>
+        <v>0.8952179141713039</v>
       </c>
     </row>
     <row r="19">
@@ -2229,11 +2229,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SIFT4G</t>
+          <t>ESM1b</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.8856343446412104</v>
+        <v>0.8925839592547476</v>
       </c>
     </row>
     <row r="20">
@@ -2248,11 +2248,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>MutationAssessor</t>
+          <t>SIFT4G</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.8847060764096328</v>
+        <v>0.8856343446412104</v>
       </c>
     </row>
     <row r="21">
@@ -2267,11 +2267,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>SIFT</t>
+          <t>MutationAssessor</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.8759753306260586</v>
+        <v>0.8847060764096328</v>
       </c>
     </row>
     <row r="22">
@@ -2286,11 +2286,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Polyphen2_HDIV</t>
+          <t>Eigen-PC-raw_coding</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.8749683863558004</v>
+        <v>0.8787234623533908</v>
       </c>
     </row>
     <row r="23">
@@ -2305,11 +2305,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>DEOGEN2</t>
+          <t>SIFT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.8438443243115672</v>
+        <v>0.8759753306260586</v>
       </c>
     </row>
     <row r="24">
@@ -2324,11 +2324,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>MVP</t>
+          <t>Polyphen2_HDIV</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.8379097880773501</v>
+        <v>0.8749683863558004</v>
       </c>
     </row>
     <row r="25">
@@ -2343,11 +2343,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>fathmm-XF_coding</t>
+          <t>CADD_raw</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.8343031034544088</v>
+        <v>0.8724303163026159</v>
       </c>
     </row>
     <row r="26">
@@ -2362,11 +2362,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>MetaSVM</t>
+          <t>DEOGEN2</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.8295207318808392</v>
+        <v>0.8438443243115672</v>
       </c>
     </row>
     <row r="27">
@@ -2381,11 +2381,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>M-CAP</t>
+          <t>MVP</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.8244641129236377</v>
+        <v>0.8379097880773501</v>
       </c>
     </row>
     <row r="28">
@@ -2400,11 +2400,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LIST-S2</t>
+          <t>fathmm-XF_coding</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.8021112498711653</v>
+        <v>0.8343031034544088</v>
       </c>
     </row>
     <row r="29">
@@ -2419,11 +2419,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>MetaLR</t>
+          <t>MetaSVM</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.7980644611361889</v>
+        <v>0.8295207318808392</v>
       </c>
     </row>
     <row r="30">
@@ -2438,11 +2438,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>PrimateAI</t>
+          <t>M-CAP</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.7800654912999023</v>
+        <v>0.8244641129236377</v>
       </c>
     </row>
     <row r="31">
@@ -2457,11 +2457,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>DANN</t>
+          <t>LIST-S2</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.7770662354337097</v>
+        <v>0.8021112498711653</v>
       </c>
     </row>
     <row r="32">
@@ -2476,10 +2476,67 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t>MetaLR</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>0.7980644611361889</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>24248</v>
+      </c>
+      <c r="B33" t="n">
+        <v>14704</v>
+      </c>
+      <c r="C33" t="n">
+        <v>9544</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>PrimateAI</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>0.7800654912999023</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>24248</v>
+      </c>
+      <c r="B34" t="n">
+        <v>14704</v>
+      </c>
+      <c r="C34" t="n">
+        <v>9544</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>DANN</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0.7770662354337097</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>24248</v>
+      </c>
+      <c r="B35" t="n">
+        <v>14704</v>
+      </c>
+      <c r="C35" t="n">
+        <v>9544</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
           <t>MutFormer</t>
         </is>
       </c>
-      <c r="E32" t="n">
+      <c r="E35" t="n">
         <v>0.7540101371449981</v>
       </c>
     </row>
@@ -2494,7 +2551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2916,11 +2973,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ESM1b</t>
+          <t>Eigen-raw_coding</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.922076782321089</v>
+        <v>0.9240274035504863</v>
       </c>
     </row>
     <row r="23">
@@ -2935,11 +2992,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>PROVEAN</t>
+          <t>ESM1b</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.9121227910163276</v>
+        <v>0.922076782321089</v>
       </c>
     </row>
     <row r="24">
@@ -2954,11 +3011,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>fathmm-XF_coding</t>
+          <t>PROVEAN</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.9111574022704096</v>
+        <v>0.9121227910163276</v>
       </c>
     </row>
     <row r="25">
@@ -2973,11 +3030,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Polyphen2_HVAR</t>
+          <t>fathmm-XF_coding</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.9055156307870895</v>
+        <v>0.9111574022704096</v>
       </c>
     </row>
     <row r="26">
@@ -2992,11 +3049,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>MutationAssessor</t>
+          <t>Eigen-PC-raw_coding</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.904259151747289</v>
+        <v>0.9102340409211652</v>
       </c>
     </row>
     <row r="27">
@@ -3011,11 +3068,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>SIFT</t>
+          <t>CADD_raw</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.8935850284216631</v>
+        <v>0.9092242518451388</v>
       </c>
     </row>
     <row r="28">
@@ -3030,11 +3087,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>SIFT4G</t>
+          <t>Polyphen2_HVAR</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.8861352483546779</v>
+        <v>0.9055156307870895</v>
       </c>
     </row>
     <row r="29">
@@ -3049,11 +3106,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Polyphen2_HDIV</t>
+          <t>MutationAssessor</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.8804860491974863</v>
+        <v>0.904259151747289</v>
       </c>
     </row>
     <row r="30">
@@ -3068,11 +3125,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LIST-S2</t>
+          <t>SIFT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.8704923805499629</v>
+        <v>0.8935850284216631</v>
       </c>
     </row>
     <row r="31">
@@ -3087,11 +3144,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>PrimateAI</t>
+          <t>SIFT4G</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.8591496377968787</v>
+        <v>0.8861352483546779</v>
       </c>
     </row>
     <row r="32">
@@ -3106,10 +3163,67 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t>Polyphen2_HDIV</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8804860491974863</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>85896</v>
+      </c>
+      <c r="B33" t="n">
+        <v>25206</v>
+      </c>
+      <c r="C33" t="n">
+        <v>60690</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LIST-S2</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>0.8704923805499629</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>85896</v>
+      </c>
+      <c r="B34" t="n">
+        <v>25206</v>
+      </c>
+      <c r="C34" t="n">
+        <v>60690</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>PrimateAI</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8591496377968787</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>85896</v>
+      </c>
+      <c r="B35" t="n">
+        <v>25206</v>
+      </c>
+      <c r="C35" t="n">
+        <v>60690</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
           <t>DANN</t>
         </is>
       </c>
-      <c r="E32" t="n">
+      <c r="E35" t="n">
         <v>0.8200577676590143</v>
       </c>
     </row>
@@ -3124,7 +3238,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3565,11 +3679,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>PROVEAN</t>
+          <t>Eigen-raw_coding</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.9018320160484994</v>
+        <v>0.9109464861413883</v>
       </c>
     </row>
     <row r="24">
@@ -3584,11 +3698,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>fathmm-XF_coding</t>
+          <t>CADD_raw</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.8979770302753129</v>
+        <v>0.9031362978546039</v>
       </c>
     </row>
     <row r="25">
@@ -3603,11 +3717,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Polyphen2_HVAR</t>
+          <t>PROVEAN</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.8924264619195501</v>
+        <v>0.9018320160484994</v>
       </c>
     </row>
     <row r="26">
@@ -3622,11 +3736,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>MutationAssessor</t>
+          <t>fathmm-XF_coding</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.8898891530622219</v>
+        <v>0.8979770302753129</v>
       </c>
     </row>
     <row r="27">
@@ -3641,11 +3755,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>SIFT</t>
+          <t>Eigen-PC-raw_coding</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.8784542382739889</v>
+        <v>0.8928145862201892</v>
       </c>
     </row>
     <row r="28">
@@ -3660,11 +3774,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>SIFT4G</t>
+          <t>Polyphen2_HVAR</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.8719994218997774</v>
+        <v>0.8924264619195501</v>
       </c>
     </row>
     <row r="29">
@@ -3679,11 +3793,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Polyphen2_HDIV</t>
+          <t>MutationAssessor</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.8673155352176152</v>
+        <v>0.8898891530622219</v>
       </c>
     </row>
     <row r="30">
@@ -3698,11 +3812,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LIST-S2</t>
+          <t>SIFT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.8582698908098532</v>
+        <v>0.8784542382739889</v>
       </c>
     </row>
     <row r="31">
@@ -3717,11 +3831,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>PrimateAI</t>
+          <t>SIFT4G</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.8402489623124284</v>
+        <v>0.8719994218997774</v>
       </c>
     </row>
     <row r="32">
@@ -3736,11 +3850,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>DANN</t>
+          <t>Polyphen2_HDIV</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.8029455267415402</v>
+        <v>0.8673155352176152</v>
       </c>
     </row>
     <row r="33">
@@ -3755,10 +3869,67 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t>LIST-S2</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>0.8582698908098532</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>25853</v>
+      </c>
+      <c r="B34" t="n">
+        <v>10961</v>
+      </c>
+      <c r="C34" t="n">
+        <v>14892</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>PrimateAI</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8402489623124284</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>25853</v>
+      </c>
+      <c r="B35" t="n">
+        <v>10961</v>
+      </c>
+      <c r="C35" t="n">
+        <v>14892</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>DANN</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0.8029455267415402</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>25853</v>
+      </c>
+      <c r="B36" t="n">
+        <v>10961</v>
+      </c>
+      <c r="C36" t="n">
+        <v>14892</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
           <t>MPC</t>
         </is>
       </c>
-      <c r="E33" t="n">
+      <c r="E36" t="n">
         <v>0.7849405235072321</v>
       </c>
     </row>
@@ -3773,7 +3944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4138,11 +4309,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>fathmm-XF_coding</t>
+          <t>CADD_raw</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.8953313659510913</v>
+        <v>0.8977875946952656</v>
       </c>
     </row>
     <row r="20">
@@ -4157,11 +4328,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ESM1b</t>
+          <t>fathmm-XF_coding</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.8877392498755391</v>
+        <v>0.8953313659510913</v>
       </c>
     </row>
     <row r="21">
@@ -4176,11 +4347,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>M-CAP</t>
+          <t>Eigen-raw_coding</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.8820927728693191</v>
+        <v>0.8932582669041921</v>
       </c>
     </row>
     <row r="22">
@@ -4195,11 +4366,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>MetaSVM</t>
+          <t>ESM1b</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.8784999010310763</v>
+        <v>0.8877392498755391</v>
       </c>
     </row>
     <row r="23">
@@ -4214,11 +4385,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>MetaLR</t>
+          <t>M-CAP</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.8706596128815551</v>
+        <v>0.8820927728693191</v>
       </c>
     </row>
     <row r="24">
@@ -4233,11 +4404,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>MutationAssessor</t>
+          <t>MetaSVM</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.8648811773103245</v>
+        <v>0.8784999010310763</v>
       </c>
     </row>
     <row r="25">
@@ -4252,11 +4423,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Polyphen2_HVAR</t>
+          <t>Eigen-PC-raw_coding</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.8548388306071893</v>
+        <v>0.8771803153809705</v>
       </c>
     </row>
     <row r="26">
@@ -4271,11 +4442,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>PROVEAN</t>
+          <t>MetaLR</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.8469063214150756</v>
+        <v>0.8706596128815551</v>
       </c>
     </row>
     <row r="27">
@@ -4290,11 +4461,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>SIFT4G</t>
+          <t>MutationAssessor</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.8436358483436202</v>
+        <v>0.8648811773103245</v>
       </c>
     </row>
     <row r="28">
@@ -4309,11 +4480,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Polyphen2_HDIV</t>
+          <t>Polyphen2_HVAR</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.8332343644095753</v>
+        <v>0.8548388306071893</v>
       </c>
     </row>
     <row r="29">
@@ -4328,11 +4499,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>SIFT</t>
+          <t>PROVEAN</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.8268366233002838</v>
+        <v>0.8469063214150756</v>
       </c>
     </row>
     <row r="30">
@@ -4347,11 +4518,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>PrimateAI</t>
+          <t>SIFT4G</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.8130379560817902</v>
+        <v>0.8436358483436202</v>
       </c>
     </row>
     <row r="31">
@@ -4366,11 +4537,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LIST-S2</t>
+          <t>Polyphen2_HDIV</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.8072790143894817</v>
+        <v>0.8332343644095753</v>
       </c>
     </row>
     <row r="32">
@@ -4385,11 +4556,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>DANN</t>
+          <t>SIFT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.7516952177016416</v>
+        <v>0.8268366233002838</v>
       </c>
     </row>
     <row r="33">
@@ -4404,11 +4575,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>MutFormer</t>
+          <t>PrimateAI</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.6851266202412443</v>
+        <v>0.8130379560817902</v>
       </c>
     </row>
     <row r="34">
@@ -4423,10 +4594,67 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t>LIST-S2</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8072790143894817</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>1895</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1428</v>
+      </c>
+      <c r="C35" t="n">
+        <v>467</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>DANN</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0.7516952177016416</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>1895</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1428</v>
+      </c>
+      <c r="C36" t="n">
+        <v>467</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>MutFormer</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>0.6851266202412443</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>1895</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1428</v>
+      </c>
+      <c r="C37" t="n">
+        <v>467</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
           <t>MPC</t>
         </is>
       </c>
-      <c r="E34" t="n">
+      <c r="E37" t="n">
         <v>0.609486621200943</v>
       </c>
     </row>
@@ -11618,7 +11846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11831,11 +12059,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>DEOGEN2</t>
+          <t>CADD_raw</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.8456820810947603</v>
+        <v>0.8863120704394017</v>
       </c>
     </row>
     <row r="12">
@@ -11850,11 +12078,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>MetaSVM</t>
+          <t>DEOGEN2</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.8390913149732685</v>
+        <v>0.8456820810947603</v>
       </c>
     </row>
     <row r="13">
@@ -11869,11 +12097,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LIST-S2</t>
+          <t>MetaSVM</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.8196858822372348</v>
+        <v>0.8390913149732685</v>
       </c>
     </row>
     <row r="14">
@@ -11888,11 +12116,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>MetaLR</t>
+          <t>LIST-S2</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.8142914099829005</v>
+        <v>0.8196858822372348</v>
       </c>
     </row>
     <row r="15">
@@ -11907,11 +12135,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>DANN</t>
+          <t>MetaLR</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.7877451533857047</v>
+        <v>0.8142914099829005</v>
       </c>
     </row>
     <row r="16">
@@ -11926,10 +12154,29 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>DANN</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0.7877451533857047</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>35119</v>
+      </c>
+      <c r="B17" t="n">
+        <v>18953</v>
+      </c>
+      <c r="C17" t="n">
+        <v>16166</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
           <t>MutFormer</t>
         </is>
       </c>
-      <c r="E16" t="n">
+      <c r="E17" t="n">
         <v>0.7714741696903804</v>
       </c>
     </row>
@@ -11944,7 +12191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12233,11 +12480,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>PROVEAN</t>
+          <t>CADD_raw</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.915286118996115</v>
+        <v>0.9155100356778325</v>
       </c>
     </row>
     <row r="16">
@@ -12252,11 +12499,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>fathmm-XF_coding</t>
+          <t>PROVEAN</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.9147293036567955</v>
+        <v>0.915286118996115</v>
       </c>
     </row>
     <row r="17">
@@ -12271,11 +12518,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LIST-S2</t>
+          <t>fathmm-XF_coding</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.8790637799781149</v>
+        <v>0.9147293036567955</v>
       </c>
     </row>
     <row r="18">
@@ -12290,11 +12537,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>PrimateAI</t>
+          <t>LIST-S2</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.8708849038130174</v>
+        <v>0.8790637799781149</v>
       </c>
     </row>
     <row r="19">
@@ -12309,10 +12556,29 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>PrimateAI</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0.8708849038130174</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>124612</v>
+      </c>
+      <c r="B20" t="n">
+        <v>37332</v>
+      </c>
+      <c r="C20" t="n">
+        <v>87280</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
           <t>DANN</t>
         </is>
       </c>
-      <c r="E19" t="n">
+      <c r="E20" t="n">
         <v>0.8221928580093816</v>
       </c>
     </row>
@@ -12327,7 +12593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12635,11 +12901,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>PROVEAN</t>
+          <t>Eigen-raw_coding</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.9101135444056029</v>
+        <v>0.9197742387093911</v>
       </c>
     </row>
     <row r="17">
@@ -12654,11 +12920,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>fathmm-XF_coding</t>
+          <t>CADD_raw</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.9095194897019014</v>
+        <v>0.9142703234235133</v>
       </c>
     </row>
     <row r="18">
@@ -12673,11 +12939,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Polyphen2_HVAR</t>
+          <t>PROVEAN</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.9003061869193041</v>
+        <v>0.9101135444056029</v>
       </c>
     </row>
     <row r="19">
@@ -12692,11 +12958,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SIFT</t>
+          <t>fathmm-XF_coding</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.8891278745136825</v>
+        <v>0.9095194897019014</v>
       </c>
     </row>
     <row r="20">
@@ -12711,11 +12977,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SIFT4G</t>
+          <t>Eigen-PC-raw_coding</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.8800158702550014</v>
+        <v>0.9034579420103657</v>
       </c>
     </row>
     <row r="21">
@@ -12730,11 +12996,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Polyphen2_HDIV</t>
+          <t>Polyphen2_HVAR</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.8759205779060144</v>
+        <v>0.9003061869193041</v>
       </c>
     </row>
     <row r="22">
@@ -12749,11 +13015,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LIST-S2</t>
+          <t>SIFT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.8726563904522296</v>
+        <v>0.8891278745136825</v>
       </c>
     </row>
     <row r="23">
@@ -12768,11 +13034,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>PrimateAI</t>
+          <t>SIFT4G</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.8540135890284759</v>
+        <v>0.8800158702550014</v>
       </c>
     </row>
     <row r="24">
@@ -12787,10 +13053,67 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>Polyphen2_HDIV</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0.8759205779060144</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>35096</v>
+      </c>
+      <c r="B25" t="n">
+        <v>12592</v>
+      </c>
+      <c r="C25" t="n">
+        <v>22504</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LIST-S2</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>0.8726563904522296</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>35096</v>
+      </c>
+      <c r="B26" t="n">
+        <v>12592</v>
+      </c>
+      <c r="C26" t="n">
+        <v>22504</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>PrimateAI</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0.8540135890284759</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>35096</v>
+      </c>
+      <c r="B27" t="n">
+        <v>12592</v>
+      </c>
+      <c r="C27" t="n">
+        <v>22504</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
           <t>DANN</t>
         </is>
       </c>
-      <c r="E24" t="n">
+      <c r="E27" t="n">
         <v>0.8189389671823415</v>
       </c>
     </row>
@@ -12805,7 +13128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13094,11 +13417,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ESM1b</t>
+          <t>CADD_raw</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.890011166177595</v>
+        <v>0.8938690540765809</v>
       </c>
     </row>
     <row r="16">
@@ -13113,11 +13436,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>MetaSVM</t>
+          <t>Eigen-raw_coding</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.8803975370904963</v>
+        <v>0.8919969994205231</v>
       </c>
     </row>
     <row r="17">
@@ -13132,11 +13455,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>M-CAP</t>
+          <t>ESM1b</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.8789891963262747</v>
+        <v>0.890011166177595</v>
       </c>
     </row>
     <row r="18">
@@ -13151,11 +13474,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>MetaLR</t>
+          <t>MetaSVM</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.8734973949995635</v>
+        <v>0.8803975370904963</v>
       </c>
     </row>
     <row r="19">
@@ -13170,11 +13493,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>MutationAssessor</t>
+          <t>M-CAP</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.8681789075668053</v>
+        <v>0.8789891963262747</v>
       </c>
     </row>
     <row r="20">
@@ -13189,11 +13512,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Polyphen2_HVAR</t>
+          <t>Eigen-PC-raw_coding</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.8590905121888619</v>
+        <v>0.8752351644629782</v>
       </c>
     </row>
     <row r="21">
@@ -13208,11 +13531,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>PROVEAN</t>
+          <t>MetaLR</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.8510492767121692</v>
+        <v>0.8734973949995635</v>
       </c>
     </row>
     <row r="22">
@@ -13227,11 +13550,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SIFT4G</t>
+          <t>MutationAssessor</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.8470855482672579</v>
+        <v>0.8681789075668053</v>
       </c>
     </row>
     <row r="23">
@@ -13246,11 +13569,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Polyphen2_HDIV</t>
+          <t>Polyphen2_HVAR</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.8363083346783902</v>
+        <v>0.8590905121888619</v>
       </c>
     </row>
     <row r="24">
@@ -13265,11 +13588,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>SIFT</t>
+          <t>PROVEAN</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.8282227784730913</v>
+        <v>0.8510492767121692</v>
       </c>
     </row>
     <row r="25">
@@ -13284,11 +13607,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LIST-S2</t>
+          <t>SIFT4G</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.8069871959399567</v>
+        <v>0.8470855482672579</v>
       </c>
     </row>
     <row r="26">
@@ -13303,11 +13626,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>PrimateAI</t>
+          <t>Polyphen2_HDIV</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.7822423378059784</v>
+        <v>0.8363083346783902</v>
       </c>
     </row>
     <row r="27">
@@ -13322,11 +13645,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>DANN</t>
+          <t>SIFT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.7530184400691138</v>
+        <v>0.8282227784730913</v>
       </c>
     </row>
     <row r="28">
@@ -13341,10 +13664,67 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t>LIST-S2</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>0.8069871959399567</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>1979</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1462</v>
+      </c>
+      <c r="C29" t="n">
+        <v>517</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>PrimateAI</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>0.7822423378059784</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>1979</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1462</v>
+      </c>
+      <c r="C30" t="n">
+        <v>517</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>DANN</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>0.7530184400691138</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>1979</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1462</v>
+      </c>
+      <c r="C31" t="n">
+        <v>517</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
           <t>MutFormer</t>
         </is>
       </c>
-      <c r="E28" t="n">
+      <c r="E31" t="n">
         <v>0.6897218245851712</v>
       </c>
     </row>
